--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-practitionerrole.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -295,17 +295,207 @@
 </t>
   </si>
   <si>
+    <t>PractitionerRole.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.extension:as-data-trace</t>
+  </si>
+  <si>
+    <t>as-data-trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+</t>
+  </si>
+  <si>
+    <t>DataTrace</t>
+  </si>
+  <si>
+    <t>Informe sur l'origine de la donnée (Autorité d'Enregistrement (AE) et Système d'Information (SI))..</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>PractitionerRole.implicitRules</t>
+    <t>PractitionerRole.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>PractitionerRole.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>PractitionerRole.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -395,38 +585,10 @@
     <t>PractitionerRole.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>PractitionerRole.extension:serviceTypeDuration</t>
@@ -451,7 +613,7 @@
     <t>as-ext-practitionerrole-name</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-name}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-name}
 </t>
   </si>
   <si>
@@ -470,7 +632,7 @@
     <t>as-ext-practitionerrole-registration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration}
 </t>
   </si>
   <si>
@@ -489,7 +651,7 @@
     <t>as-ext-practitionerrole-education-level</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-education-level}
 </t>
   </si>
   <si>
@@ -505,7 +667,7 @@
     <t>as-ext-practitionerrole-smartcard</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-smartcard}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-smartcard}
 </t>
   </si>
   <si>
@@ -525,7 +687,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
 </t>
   </si>
   <si>
@@ -541,7 +703,7 @@
     <t>as-ext-practitionerrole-end-cause</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-end-cause}
 </t>
   </si>
   <si>
@@ -560,7 +722,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted}
 </t>
   </si>
   <si>
@@ -579,7 +741,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas}
 </t>
   </si>
   <si>
@@ -598,7 +760,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted}
 </t>
   </si>
   <si>
@@ -649,26 +811,7 @@
     <t>PractitionerRole.identifier.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>PractitionerRole.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>PractitionerRole.identifier.use</t>
@@ -717,9 +860,6 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -959,10 +1099,6 @@
     <t>PractitionerRole.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Code defined by a terminology system</t>
   </si>
   <si>
@@ -1246,7 +1382,7 @@
     <t>PractitionerRole.specialty</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
+    <t xml:space="preserve">CodeableConcept {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-codeableconcept-timed}
 </t>
   </si>
   <si>
@@ -1505,7 +1641,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
 </t>
   </si>
   <si>
@@ -1975,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ89"/>
+  <dimension ref="A1:AJ98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.21484375" customWidth="true" bestFit="true"/>
@@ -1988,7 +2124,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="108.7421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2424,15 +2560,15 @@
         <v>90</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2449,23 +2585,21 @@
         <v>71</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="M5" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>71</v>
@@ -2514,7 +2648,7 @@
         <v>71</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>72</v>
@@ -2523,29 +2657,29 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>71</v>
@@ -2557,16 +2691,16 @@
         <v>71</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2592,43 +2726,43 @@
         <v>71</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AC6" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" hidden="true">
@@ -2636,11 +2770,13 @@
         <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="D7" t="s" s="2">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2650,7 +2786,7 @@
         <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>71</v>
@@ -2667,9 +2803,7 @@
       <c r="M7" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="N7" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>71</v>
@@ -2718,38 +2852,38 @@
         <v>71</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>71</v>
@@ -2758,19 +2892,19 @@
         <v>71</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2820,38 +2954,38 @@
         <v>71</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>71</v>
@@ -2860,19 +2994,19 @@
         <v>71</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2910,52 +3044,50 @@
         <v>71</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>71</v>
@@ -2964,19 +3096,19 @@
         <v>71</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3026,31 +3158,29 @@
         <v>71</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>71</v>
       </c>
@@ -3062,25 +3192,25 @@
         <v>73</v>
       </c>
       <c r="H11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3130,7 +3260,7 @@
         <v>71</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>72</v>
@@ -3142,19 +3272,17 @@
         <v>90</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>71</v>
       </c>
@@ -3166,25 +3294,25 @@
         <v>73</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3210,13 +3338,13 @@
         <v>71</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>71</v>
@@ -3234,7 +3362,7 @@
         <v>71</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>72</v>
@@ -3246,19 +3374,17 @@
         <v>90</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>71</v>
       </c>
@@ -3270,24 +3396,26 @@
         <v>73</v>
       </c>
       <c r="H13" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I13" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="K13" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>71</v>
@@ -3312,13 +3440,13 @@
         <v>71</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>71</v>
+        <v>149</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>71</v>
@@ -3336,7 +3464,7 @@
         <v>71</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>72</v>
@@ -3348,19 +3476,17 @@
         <v>90</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>155</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>71</v>
       </c>
@@ -3369,28 +3495,28 @@
         <v>72</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3440,31 +3566,29 @@
         <v>71</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>71</v>
       </c>
@@ -3473,10 +3597,10 @@
         <v>72</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>71</v>
@@ -3485,15 +3609,17 @@
         <v>71</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>71</v>
@@ -3518,13 +3644,13 @@
         <v>71</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>71</v>
@@ -3542,33 +3668,31 @@
         <v>71</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3578,7 +3702,7 @@
         <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>71</v>
@@ -3587,16 +3711,16 @@
         <v>71</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3646,43 +3770,41 @@
         <v>71</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>71</v>
@@ -3691,16 +3813,16 @@
         <v>71</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3750,7 +3872,7 @@
         <v>71</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>72</v>
@@ -3759,34 +3881,32 @@
         <v>73</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>71</v>
@@ -3795,16 +3915,16 @@
         <v>71</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3842,19 +3962,19 @@
         <v>71</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>72</v>
@@ -3866,31 +3986,31 @@
         <v>90</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>71</v>
@@ -3899,16 +4019,16 @@
         <v>71</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3958,7 +4078,7 @@
         <v>71</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>72</v>
@@ -3970,7 +4090,7 @@
         <v>90</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -3978,11 +4098,13 @@
         <v>189</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3992,29 +4114,27 @@
         <v>73</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>71</v>
       </c>
@@ -4050,19 +4170,19 @@
         <v>71</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>72</v>
@@ -4074,17 +4194,19 @@
         <v>90</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>71</v>
       </c>
@@ -4102,23 +4224,21 @@
         <v>71</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>71</v>
       </c>
@@ -4166,7 +4286,7 @@
         <v>71</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>72</v>
@@ -4178,17 +4298,19 @@
         <v>90</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>71</v>
       </c>
@@ -4197,10 +4319,10 @@
         <v>72</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>71</v>
@@ -4209,13 +4331,13 @@
         <v>71</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4266,31 +4388,33 @@
         <v>71</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4300,7 +4424,7 @@
         <v>73</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>71</v>
@@ -4309,16 +4433,16 @@
         <v>71</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>124</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>126</v>
+        <v>211</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4356,19 +4480,19 @@
         <v>71</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>72</v>
@@ -4380,17 +4504,19 @@
         <v>90</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>71</v>
       </c>
@@ -4399,32 +4525,28 @@
         <v>72</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>71</v>
       </c>
@@ -4448,13 +4570,13 @@
         <v>71</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>214</v>
+        <v>71</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>215</v>
+        <v>71</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>71</v>
@@ -4472,19 +4594,19 @@
         <v>71</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4492,9 +4614,11 @@
         <v>217</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>71</v>
       </c>
@@ -4506,29 +4630,27 @@
         <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O25" t="s" s="2">
         <v>222</v>
       </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>71</v>
       </c>
@@ -4552,13 +4674,13 @@
         <v>71</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>223</v>
+        <v>71</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>71</v>
@@ -4576,29 +4698,31 @@
         <v>71</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>71</v>
       </c>
@@ -4610,29 +4734,27 @@
         <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>71</v>
       </c>
@@ -4644,7 +4766,7 @@
         <v>71</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>232</v>
+        <v>71</v>
       </c>
       <c r="U26" t="s" s="2">
         <v>71</v>
@@ -4680,29 +4802,31 @@
         <v>71</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>71</v>
       </c>
@@ -4714,25 +4838,25 @@
         <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4746,7 +4870,7 @@
         <v>71</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>238</v>
+        <v>71</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>71</v>
@@ -4782,29 +4906,31 @@
         <v>71</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>71</v>
       </c>
@@ -4816,25 +4942,25 @@
         <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4884,61 +5010,63 @@
         <v>71</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>246</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>98</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>71</v>
       </c>
@@ -4974,39 +5102,39 @@
         <v>71</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>253</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5017,7 +5145,7 @@
         <v>72</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>79</v>
@@ -5029,26 +5157,24 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q30" t="s" s="2">
-        <v>260</v>
-      </c>
+      <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
         <v>71</v>
       </c>
@@ -5092,27 +5218,27 @@
         <v>71</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5126,29 +5252,25 @@
         <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>241</v>
+        <v>92</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>93</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>71</v>
       </c>
@@ -5196,7 +5318,7 @@
         <v>71</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>95</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>72</v>
@@ -5205,29 +5327,29 @@
         <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>246</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>71</v>
@@ -5239,15 +5361,17 @@
         <v>71</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>202</v>
+        <v>99</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>71</v>
@@ -5284,73 +5408,75 @@
         <v>71</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>124</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>71</v>
       </c>
@@ -5374,51 +5500,51 @@
         <v>71</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>71</v>
+        <v>260</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>71</v>
+        <v>261</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5441,18 +5567,20 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>71</v>
       </c>
@@ -5476,13 +5604,13 @@
         <v>71</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>71</v>
+        <v>269</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>71</v>
+        <v>270</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>71</v>
@@ -5500,7 +5628,7 @@
         <v>71</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>72</v>
@@ -5509,18 +5637,18 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>273</v>
+        <v>90</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5543,68 +5671,68 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="P35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T35" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="O35" s="2"/>
-      <c r="P35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q35" t="s" s="2">
+      <c r="U35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="R35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>72</v>
@@ -5613,18 +5741,18 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>273</v>
+        <v>90</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5638,7 +5766,7 @@
         <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>71</v>
@@ -5647,16 +5775,16 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5670,7 +5798,7 @@
         <v>71</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>71</v>
+        <v>283</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>71</v>
@@ -5706,7 +5834,7 @@
         <v>71</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>72</v>
@@ -5718,7 +5846,7 @@
         <v>90</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -5740,7 +5868,7 @@
         <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>71</v>
@@ -5808,7 +5936,7 @@
         <v>71</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>72</v>
@@ -5820,15 +5948,15 @@
         <v>90</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>253</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5839,7 +5967,7 @@
         <v>72</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>71</v>
@@ -5851,20 +5979,18 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>218</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>71</v>
       </c>
@@ -5888,13 +6014,13 @@
         <v>71</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>296</v>
+        <v>71</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>71</v>
@@ -5912,27 +6038,27 @@
         <v>71</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>71</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5946,29 +6072,35 @@
         <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>202</v>
+        <v>301</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q39" s="2"/>
+      <c r="Q39" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="R39" t="s" s="2">
         <v>71</v>
       </c>
@@ -6012,7 +6144,7 @@
         <v>71</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>204</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>72</v>
@@ -6021,52 +6153,54 @@
         <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>123</v>
+        <v>286</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>124</v>
+        <v>307</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>71</v>
       </c>
@@ -6102,39 +6236,39 @@
         <v>71</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>131</v>
+        <v>291</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6145,7 +6279,7 @@
         <v>72</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>71</v>
@@ -6154,23 +6288,19 @@
         <v>71</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>301</v>
+        <v>93</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>71</v>
       </c>
@@ -6206,75 +6336,73 @@
         <v>71</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AC41" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>306</v>
+        <v>95</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>302</v>
+        <v>100</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>71</v>
       </c>
@@ -6298,31 +6426,31 @@
         <v>71</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>311</v>
+        <v>71</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>312</v>
+        <v>71</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>306</v>
+        <v>105</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>72</v>
@@ -6334,19 +6462,17 @@
         <v>90</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>71</v>
       </c>
@@ -6358,7 +6484,7 @@
         <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>71</v>
@@ -6367,20 +6493,18 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>71</v>
       </c>
@@ -6404,43 +6528,43 @@
         <v>71</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AG43" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI43" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AA43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="AJ43" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -6448,11 +6572,9 @@
         <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>71</v>
       </c>
@@ -6464,7 +6586,7 @@
         <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>71</v>
@@ -6473,24 +6595,24 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q44" s="2"/>
+      <c r="Q44" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="R44" t="s" s="2">
         <v>71</v>
       </c>
@@ -6510,55 +6632,53 @@
         <v>71</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>323</v>
+        <v>71</v>
       </c>
       <c r="Z44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI44" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AA44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>90</v>
-      </c>
       <c r="AJ44" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C45" t="s" s="2">
         <v>325</v>
       </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>71</v>
       </c>
@@ -6579,20 +6699,18 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>71</v>
       </c>
@@ -6616,13 +6734,13 @@
         <v>71</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>328</v>
+        <v>71</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>318</v>
+        <v>71</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>71</v>
@@ -6640,31 +6758,29 @@
         <v>71</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C46" t="s" s="2">
         <v>330</v>
       </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>71</v>
       </c>
@@ -6685,20 +6801,18 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>71</v>
       </c>
@@ -6722,13 +6836,13 @@
         <v>71</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>333</v>
+        <v>71</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>318</v>
+        <v>71</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>71</v>
@@ -6746,31 +6860,29 @@
         <v>71</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C47" t="s" s="2">
         <v>335</v>
       </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>71</v>
       </c>
@@ -6779,10 +6891,10 @@
         <v>72</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>71</v>
@@ -6791,19 +6903,19 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>71</v>
@@ -6828,13 +6940,13 @@
         <v>71</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>71</v>
@@ -6852,7 +6964,7 @@
         <v>71</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>72</v>
@@ -6864,19 +6976,17 @@
         <v>90</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>71</v>
       </c>
@@ -6888,29 +6998,25 @@
         <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>342</v>
+        <v>93</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>71</v>
       </c>
@@ -6934,13 +7040,13 @@
         <v>71</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>344</v>
+        <v>71</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>345</v>
+        <v>71</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>71</v>
@@ -6958,65 +7064,61 @@
         <v>71</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>306</v>
+        <v>95</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>99</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>302</v>
+        <v>100</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>71</v>
       </c>
@@ -7040,31 +7142,31 @@
         <v>71</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>350</v>
+        <v>71</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>351</v>
+        <v>71</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>306</v>
+        <v>105</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>72</v>
@@ -7076,19 +7178,17 @@
         <v>90</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>71</v>
       </c>
@@ -7097,10 +7197,10 @@
         <v>72</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>71</v>
@@ -7109,19 +7209,19 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>71</v>
@@ -7146,31 +7246,29 @@
         <v>71</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>356</v>
+        <v>71</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>357</v>
+        <v>71</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>72</v>
@@ -7182,18 +7280,18 @@
         <v>90</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>71</v>
@@ -7215,19 +7313,19 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>71</v>
@@ -7252,13 +7350,13 @@
         <v>71</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>71</v>
@@ -7276,7 +7374,7 @@
         <v>71</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>72</v>
@@ -7288,18 +7386,18 @@
         <v>90</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>71</v>
@@ -7321,19 +7419,19 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>71</v>
@@ -7358,13 +7456,13 @@
         <v>71</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>71</v>
@@ -7382,7 +7480,7 @@
         <v>71</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>72</v>
@@ -7394,18 +7492,18 @@
         <v>90</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>71</v>
@@ -7427,19 +7525,19 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>71</v>
@@ -7464,13 +7562,13 @@
         <v>71</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>71</v>
@@ -7488,7 +7586,7 @@
         <v>71</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>72</v>
@@ -7500,18 +7598,18 @@
         <v>90</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>71</v>
@@ -7533,19 +7631,19 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>71</v>
@@ -7570,13 +7668,13 @@
         <v>71</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>71</v>
@@ -7594,7 +7692,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -7606,18 +7704,18 @@
         <v>90</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>71</v>
@@ -7639,19 +7737,19 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>71</v>
@@ -7676,13 +7774,13 @@
         <v>71</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>71</v>
@@ -7700,7 +7798,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -7712,18 +7810,18 @@
         <v>90</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>71</v>
@@ -7745,19 +7843,19 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>71</v>
@@ -7782,13 +7880,13 @@
         <v>71</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>71</v>
@@ -7806,7 +7904,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -7818,17 +7916,19 @@
         <v>90</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>71</v>
       </c>
@@ -7840,7 +7940,7 @@
         <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>71</v>
@@ -7849,19 +7949,19 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>392</v>
+        <v>348</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>71</v>
@@ -7886,13 +7986,13 @@
         <v>71</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>71</v>
+        <v>388</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>71</v>
+        <v>389</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>71</v>
@@ -7910,29 +8010,31 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C58" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="D58" t="s" s="2">
         <v>71</v>
       </c>
@@ -7941,10 +8043,10 @@
         <v>72</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>71</v>
@@ -7953,18 +8055,20 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>71</v>
       </c>
@@ -7988,31 +8092,31 @@
         <v>71</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>401</v>
+        <v>71</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>402</v>
+        <v>71</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -8024,18 +8128,18 @@
         <v>90</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>71</v>
@@ -8045,7 +8149,7 @@
         <v>72</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -8057,18 +8161,20 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>71</v>
       </c>
@@ -8092,11 +8198,13 @@
         <v>71</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>71</v>
@@ -8114,7 +8222,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8126,18 +8234,18 @@
         <v>90</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>71</v>
@@ -8147,7 +8255,7 @@
         <v>72</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -8159,18 +8267,20 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>71</v>
       </c>
@@ -8194,13 +8304,13 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8218,7 +8328,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8230,18 +8340,18 @@
         <v>90</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>71</v>
@@ -8251,7 +8361,7 @@
         <v>72</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -8263,18 +8373,20 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>71</v>
       </c>
@@ -8298,10 +8410,10 @@
         <v>71</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="Z61" t="s" s="2">
         <v>413</v>
@@ -8322,7 +8434,7 @@
         <v>71</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>72</v>
@@ -8334,18 +8446,18 @@
         <v>90</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>71</v>
@@ -8355,7 +8467,7 @@
         <v>72</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -8367,18 +8479,20 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>71</v>
       </c>
@@ -8402,10 +8516,10 @@
         <v>71</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="Z62" t="s" s="2">
         <v>413</v>
@@ -8426,7 +8540,7 @@
         <v>71</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>72</v>
@@ -8438,18 +8552,18 @@
         <v>90</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>71</v>
@@ -8459,7 +8573,7 @@
         <v>72</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>79</v>
@@ -8471,18 +8585,20 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>71</v>
       </c>
@@ -8506,10 +8622,10 @@
         <v>71</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="Z63" t="s" s="2">
         <v>413</v>
@@ -8530,7 +8646,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8542,18 +8658,18 @@
         <v>90</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>71</v>
@@ -8563,7 +8679,7 @@
         <v>72</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -8575,18 +8691,20 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>71</v>
       </c>
@@ -8610,13 +8728,13 @@
         <v>71</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>71</v>
@@ -8634,7 +8752,7 @@
         <v>71</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>72</v>
@@ -8646,18 +8764,18 @@
         <v>90</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>394</v>
+        <v>344</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>71</v>
@@ -8667,7 +8785,7 @@
         <v>72</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
@@ -8679,18 +8797,20 @@
         <v>79</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>71</v>
       </c>
@@ -8714,13 +8834,13 @@
         <v>71</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>71</v>
@@ -8738,7 +8858,7 @@
         <v>71</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>72</v>
@@ -8750,19 +8870,17 @@
         <v>90</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>71</v>
       </c>
@@ -8771,10 +8889,10 @@
         <v>72</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>71</v>
@@ -8783,18 +8901,20 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>71</v>
       </c>
@@ -8818,13 +8938,13 @@
         <v>71</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>443</v>
+        <v>71</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>413</v>
+        <v>71</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>71</v>
@@ -8842,31 +8962,29 @@
         <v>71</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>71</v>
       </c>
@@ -8878,7 +8996,7 @@
         <v>73</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>71</v>
@@ -8887,16 +9005,16 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>218</v>
+        <v>439</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8922,31 +9040,31 @@
         <v>71</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>413</v>
+        <v>444</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>71</v>
+        <v>445</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>71</v>
+        <v>446</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -8958,18 +9076,18 @@
         <v>90</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>71</v>
@@ -8991,16 +9109,16 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9026,13 +9144,11 @@
         <v>71</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>71</v>
@@ -9050,7 +9166,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -9062,18 +9178,18 @@
         <v>90</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>71</v>
@@ -9095,16 +9211,16 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9130,13 +9246,13 @@
         <v>71</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>71</v>
@@ -9154,7 +9270,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9166,17 +9282,19 @@
         <v>90</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>71</v>
       </c>
@@ -9197,16 +9315,16 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9232,13 +9350,13 @@
         <v>71</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>71</v>
+        <v>462</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>71</v>
@@ -9256,7 +9374,7 @@
         <v>71</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>72</v>
@@ -9268,17 +9386,19 @@
         <v>90</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>71</v>
       </c>
@@ -9296,19 +9416,19 @@
         <v>71</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9334,13 +9454,13 @@
         <v>71</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>71</v>
+        <v>467</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>71</v>
@@ -9358,7 +9478,7 @@
         <v>71</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>72</v>
@@ -9370,17 +9490,19 @@
         <v>90</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>71</v>
       </c>
@@ -9401,18 +9523,18 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="L72" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>474</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>71</v>
       </c>
@@ -9436,29 +9558,31 @@
         <v>71</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>71</v>
+        <v>472</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AC72" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD72" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9470,18 +9594,18 @@
         <v>90</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>476</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>71</v>
@@ -9494,29 +9618,27 @@
         <v>73</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>479</v>
+        <v>264</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>71</v>
       </c>
@@ -9540,13 +9662,13 @@
         <v>71</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>71</v>
+        <v>477</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>71</v>
@@ -9564,7 +9686,7 @@
         <v>71</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9576,17 +9698,19 @@
         <v>90</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>476</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>71</v>
       </c>
@@ -9604,19 +9728,19 @@
         <v>71</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>483</v>
+        <v>264</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9642,13 +9766,13 @@
         <v>71</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>71</v>
+        <v>482</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>71</v>
@@ -9666,7 +9790,7 @@
         <v>71</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>438</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>72</v>
@@ -9678,17 +9802,19 @@
         <v>90</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="D75" t="s" s="2">
         <v>71</v>
       </c>
@@ -9697,27 +9823,29 @@
         <v>72</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>202</v>
+        <v>485</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>71</v>
@@ -9742,13 +9870,13 @@
         <v>71</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>71</v>
+        <v>487</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>71</v>
@@ -9766,19 +9894,19 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>204</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" hidden="true">
@@ -9786,11 +9914,13 @@
         <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="D76" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -9800,25 +9930,25 @@
         <v>73</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>124</v>
+        <v>490</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>206</v>
+        <v>441</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>126</v>
+        <v>491</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9844,31 +9974,31 @@
         <v>71</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>71</v>
+        <v>492</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>207</v>
+        <v>438</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
@@ -9880,19 +10010,21 @@
         <v>90</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>494</v>
+      </c>
       <c r="D77" t="s" s="2">
-        <v>490</v>
+        <v>71</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -9902,29 +10034,27 @@
         <v>73</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>71</v>
       </c>
@@ -9948,13 +10078,13 @@
         <v>71</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>71</v>
+        <v>497</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>71</v>
+        <v>457</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>71</v>
@@ -9972,7 +10102,7 @@
         <v>71</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>493</v>
+        <v>438</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -9984,17 +10114,19 @@
         <v>90</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>71</v>
       </c>
@@ -10006,25 +10138,25 @@
         <v>73</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>99</v>
+        <v>264</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>496</v>
+        <v>441</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10050,13 +10182,13 @@
         <v>71</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>71</v>
@@ -10074,7 +10206,7 @@
         <v>71</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>494</v>
+        <v>438</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>72</v>
@@ -10086,15 +10218,15 @@
         <v>90</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10105,27 +10237,29 @@
         <v>72</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>255</v>
+        <v>505</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>71</v>
@@ -10174,27 +10308,27 @@
         <v>71</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10205,10 +10339,10 @@
         <v>72</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>71</v>
@@ -10217,16 +10351,16 @@
         <v>71</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10276,27 +10410,27 @@
         <v>71</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>91</v>
+        <v>298</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10307,30 +10441,30 @@
         <v>72</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>71</v>
       </c>
@@ -10366,41 +10500,41 @@
         <v>71</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="AC81" s="2"/>
       <c r="AD81" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>91</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>71</v>
       </c>
@@ -10412,7 +10546,7 @@
         <v>73</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>71</v>
@@ -10421,16 +10555,20 @@
         <v>71</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>483</v>
+        <v>523</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>71</v>
       </c>
@@ -10478,7 +10616,7 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
@@ -10490,15 +10628,15 @@
         <v>90</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>91</v>
+        <v>520</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10509,10 +10647,10 @@
         <v>72</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>71</v>
@@ -10521,15 +10659,17 @@
         <v>71</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>201</v>
+        <v>527</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>202</v>
+        <v>528</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>71</v>
@@ -10578,38 +10718,38 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>204</v>
+        <v>526</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>71</v>
@@ -10621,17 +10761,15 @@
         <v>71</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>71</v>
@@ -10668,43 +10806,43 @@
         <v>71</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>490</v>
+        <v>97</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -10717,26 +10855,24 @@
         <v>71</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>491</v>
+        <v>99</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>492</v>
+        <v>100</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>71</v>
       </c>
@@ -10772,19 +10908,19 @@
         <v>71</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>105</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>72</v>
@@ -10796,49 +10932,51 @@
         <v>90</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>131</v>
+        <v>106</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>71</v>
+        <v>534</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>71</v>
       </c>
@@ -10886,27 +11024,27 @@
         <v>71</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>91</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10917,7 +11055,7 @@
         <v>72</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>71</v>
@@ -10929,16 +11067,16 @@
         <v>71</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>241</v>
+        <v>159</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>244</v>
+        <v>541</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10964,13 +11102,13 @@
         <v>71</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>71</v>
+        <v>259</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>71</v>
+        <v>542</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>71</v>
+        <v>543</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>71</v>
@@ -10988,27 +11126,27 @@
         <v>71</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>246</v>
+        <v>117</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11022,7 +11160,7 @@
         <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>71</v>
@@ -11031,17 +11169,15 @@
         <v>71</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>71</v>
@@ -11090,7 +11226,7 @@
         <v>71</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>72</v>
@@ -11102,15 +11238,15 @@
         <v>90</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11121,10 +11257,10 @@
         <v>72</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>71</v>
@@ -11133,20 +11269,18 @@
         <v>71</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>71</v>
       </c>
@@ -11194,23 +11328,941 @@
         <v>71</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>253</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ89">
+  <autoFilter ref="A1:AJ98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11220,7 +12272,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI88">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
